--- a/Vehicles-data/India-Vehicles-Master-List.xlsx
+++ b/Vehicles-data/India-Vehicles-Master-List.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vehicles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schema" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation Report" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed Rows" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Colour Families Archive" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Vehicles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Schema" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Validation Report" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Removed Rows" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Colour Families Archive" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Lists" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vehicles'!$A$1:$P$1041</definedName>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Blue; White; Cumulus Gray; Pearl White; Perla Nera Black; Tijuca Blue</t>
+          <t>Blue; White; Cumulus Gray; Pearl White; Perla Nera Black; Tijuca Blue; Eclipse Blue; Cumulus Grey</t>
         </is>
       </c>
       <c r="K21" s="3" t="n">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Golden Brown Metalli; Lunar Silver Metalli; Meteoroid Grey Metal; Platinum White Pearl; Radiant Red Metallic</t>
+          <t>Golden Brown Metalli; Lunar Silver Metalli; Meteoroid Grey Metal; Platinum White Pearl; Radiant Red Metallic; Obsidian Blue Pearl</t>
         </is>
       </c>
       <c r="K56" s="3" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Golden Brown Metalli; Lunar Silver Metalli; Modern Steel Metalli; Platinum White Pear; Rediant Red Metallic</t>
+          <t>Golden Brown Metallic; Lunar Silver Metallic; Modern Steel Metallic; Platinum White Pearl; Rediant Red Metallic</t>
         </is>
       </c>
       <c r="K57" s="3" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Golden Brown Metalli; Lunar Silver Metalli; Modern Steel Metalli; Platinum White Pearl; Premium Amber Metall; Rediant Red Metallic</t>
+          <t>Golden Brown Metallic; Lunar Silver Metallic; Modern Steel Metallic; Platinum White Pearl; Premium Amber Metallic; Rediant Red Metallic</t>
         </is>
       </c>
       <c r="K58" s="3" t="n">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Phoenix Orange Pearl; Golden Brown Metalli; Meteoroid Grey Metal; Platinum White Pearl; Lunar Silver Metalli; Obsidian Blue Pearl; Radiant Red Metallic; Radiant Red-Metallic</t>
+          <t>Phoenix Orange Pearl; Golden Brown Metalli; Meteoroid Grey Metal; Platinum White Pearl; Lunar Silver Metalli; Obsidian Blue Pearl; Radiant Red Metallic; Radiant Red-Metallic; Meteoroid Gray</t>
         </is>
       </c>
       <c r="K62" s="3" t="n">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Lunar Silver Metalli; Golden Brown Metalli; Meteoroid Grey Metal; Obsidian Blue Pearl; Platinum White Pearl; Rediant Red Metallic</t>
+          <t>Lunar Silver Metalli; Golden Brown Metalli; Meteoroid Grey Metal; Obsidian Blue Pearl; Platinum White Pearl; Rediant Red Metallic; Radiant Red</t>
         </is>
       </c>
       <c r="K66" s="3" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Oberon Black; Pebble Gray; Seaweed Green; Sunlit Yellow Black; Sunlit Yellow; Ash Gray; Coral Red; Black</t>
+          <t>Oberon Black; Pebble Gray; Seaweed Green; Sunlit Yellow Black; Sunlit Yellow; Ash Gray; Coral Red; Black; Titan Grey; Mystic Sapphire; Hazel Blue; Dragon Red; Atlas White; Abyss Black</t>
         </is>
       </c>
       <c r="K78" s="3" t="n">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Oberon Black; Pebble Gray; Seaweed Green; Sunlit Yellow Black; Sunlit Yellow; Ash Gray; Coral Red; Black</t>
+          <t>Oberon Black; Pebble Gray; Seaweed Green; Sunlit Yellow Black; Sunlit Yellow; Ash Gray; Coral Red; Black; Titan Grey; Mystic Sapphire; Hazel Blue; Dragon Red; Atlas White; Abyss Black</t>
         </is>
       </c>
       <c r="K79" s="3" t="n">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Oberon Black; Pebble Gray; Seaweed Green; Sunlit Yellow Black; Sunlit Yellow; Ash Gray; Coral Red; Black</t>
+          <t>Oberon Black; Pebble Gray; Seaweed Green; Sunlit Yellow Black; Sunlit Yellow; Ash Gray; Coral Red; Black; Titan Grey; Mystic Sapphire; Hazel Blue; Dragon Red; Atlas White; Abyss Black</t>
         </is>
       </c>
       <c r="K80" s="3" t="n">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Fiery Red; Typhoon Silver; Starry Night; Atlas White; Titan Grey; Tellurian Brow; Abyss Black</t>
+          <t>Fiery Red; Typhoon Silver; Starry Night; Atlas White; Titan Grey; Tellurian Brown; Abyss Black; Titanium Black; Classy Blue; Titan Grey (Matte &amp; regular)</t>
         </is>
       </c>
       <c r="K81" s="3" t="n">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Fiery Red; Typhoon Silver; Starry Night; Atlas White; Titan Grey; Tellurian Brow; Abyss Black</t>
+          <t>Fiery Red; Typhoon Silver; Starry Night; Atlas White; Titan Grey; Tellurian Brown; Abyss Black; Titanium Black; Classy Blue; Titan Grey (Matte &amp; regular)</t>
         </is>
       </c>
       <c r="K82" s="3" t="n">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Fiery Red; Typhoon Silver; Starry Night; Atlas White; Titan Grey; Tellurian Brow; Abyss Black</t>
+          <t>Fiery Red; Typhoon Silver; Starry Night; Atlas White; Titan Grey; Tellurian Brown; Abyss Black; Titanium Black; Classy Blue; Titan Grey (Matte &amp; regular)</t>
         </is>
       </c>
       <c r="K83" s="3" t="n">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>i20 Fiery Red; i20 Typhoon Silver; i20 Starry Night; i20 Atlas White; i20 Titan Grey; i20 Amazon Grey</t>
+          <t>i20 Fiery Red; i20 Typhoon Silver; i20 Starry Night; i20 Atlas White; i20 Titan Grey; i20 Amazon Grey; Titan Grey; Optic White; Midnight Black Pearl; Gravity Gold Matte</t>
         </is>
       </c>
       <c r="K101" s="3" t="n">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>i20 Fiery Red; i20 Typhoon Silver; i20 Starry Night; i20 Atlas White; i20 Titan Grey; i20 Amazon Grey</t>
+          <t>i20 Fiery Red; i20 Typhoon Silver; i20 Starry Night; i20 Atlas White; i20 Titan Grey; i20 Amazon Grey; Titan Grey; Optic White; Midnight Black Pearl; Gravity Gold Matte</t>
         </is>
       </c>
       <c r="K102" s="3" t="n">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>Galaxy Blue; Pearl White; Brilliant Black; Grigo Magnesio Grey; Exotica Red; Techno Metallic Gree; Silvery Moon</t>
+          <t>Galaxy Blue; Pearl White; Brilliant Black; Grigo Magnesio Grey; Exotica Red; Techno Metallic Green; Silvery Moon</t>
         </is>
       </c>
       <c r="K111" s="3" t="n">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Velvet Red; Galaxy Blue; Minimal Grey; Silver Moon; Black Magnesio; Brilliant Black; magnesio Grey; Pearl White; Techno Metallic Gree</t>
+          <t>Velvet Red; Galaxy Blue; Minimal Grey; Silver Moon; Black Magnesio; Brilliant Black; magnesio Grey; Pearl White; Techno Metallic Green; Brilliant Blue; Silvery Moon</t>
         </is>
       </c>
       <c r="K112" s="3" t="n">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>Black; Bright White; Fire Cracker Red; Galaxy Blue; Granite Crystal</t>
+          <t>Black; Bright White; Fire Cracker Red; Galaxy Blue; Granite Crystal; Billet Silver; Deep Cherry Red; Techno Metallic Green</t>
         </is>
       </c>
       <c r="K113" s="3" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>Rocky; Diamo; Velve; Brigh</t>
+          <t>Rocky; Diamond Black Crystal; Velvet Red; Bright White; Rocky Mountain</t>
         </is>
       </c>
       <c r="K114" s="3" t="n">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>Pewter Olive; Aurora Black Pearl; Glacier White Pearl; Intense Red; Sparkling Silver; Gravity Gray; Imperial Blue</t>
+          <t>Pewter Olive; Aurora Black Pearl; Glacier White Pearl; Intense Red; Sparkling Silver; Gravity Gray; Imperial Blue; Matte Graphite; Ivory Silver Matte; Magma Red; Morning Haze; Frost Blue</t>
         </is>
       </c>
       <c r="K115" s="3" t="n">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Pewter Olive; Aurora Black Pearl; Glacier White Pearl; Intense Red; Sparkling Silver; Gravity Gray; Imperial Blue</t>
+          <t>Pewter Olive; Aurora Black Pearl; Glacier White Pearl; Intense Red; Sparkling Silver; Gravity Gray; Imperial Blue; Matte Graphite; Ivory Silver Matte; Magma Red; Morning Haze; Frost Blue</t>
         </is>
       </c>
       <c r="K116" s="3" t="n">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>Pewter Olive; Aurora Black Pearl; Glacier White Pearl; Intense Red; Sparkling Silver; Gravity Gray; Imperial Blue</t>
+          <t>Pewter Olive; Aurora Black Pearl; Glacier White Pearl; Intense Red; Sparkling Silver; Gravity Gray; Imperial Blue; Matte Graphite; Ivory Silver Matte; Magma Red; Morning Haze; Frost Blue</t>
         </is>
       </c>
       <c r="K117" s="3" t="n">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>Aurora Black Pearl; Beige Gold; Glacier White Pearl; Gravity Gray; Intelligence Blue; Intense Red</t>
+          <t>Aurora Black Pearl; Beige Gold; Glacier White Pearl; Gravity Gray; Intelligence Blue; Intense Red; Sparkling Silver; Gravity Grey; Imperial Blue; Pewter Olive</t>
         </is>
       </c>
       <c r="K118" s="3" t="n">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>Aurora Black Pearl; Glacier White Pearl; Intense Red; Gravity Gray; Imperial Blue; Sparkling Silver</t>
+          <t>Aurora Black Pearl; Glacier White Pearl; Intense Red; Gravity Gray; Imperial Blue; Sparkling Silver; Clear White; Gravity Grey; Moss Brown</t>
         </is>
       </c>
       <c r="K119" s="3" t="n">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>Aurora Black Pearl; Glacier White Pearl; Steel Silver</t>
+          <t>Aurora Black Pearl; Glacier White Pearl; Steel Silver; Fusion Black</t>
         </is>
       </c>
       <c r="K120" s="3" t="n">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>Glacier White Pearl; Sparkling Silver; Pewter Olive; Intense Red; Frost Blue; Aurora Black Pearl; Imperial Blue; Gravity Gray</t>
+          <t>Glacier White Pearl; Sparkling Silver; Pewter Olive; Intense Red; Frost Blue; Aurora Black Pearl; Imperial Blue; Gravity Gray; Gravity Grey</t>
         </is>
       </c>
       <c r="K121" s="3" t="n">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>Glacie; Sparkl; Ivory; Pewter; Aurora; Imperi; Gravit</t>
+          <t>Glacier White Pearl; Sparkling Silver; Ivory; Pewter; Aurora; Imperial Blue; Gravity Gray; Pewter Olive; Aurora Black Pearl; Ivory Silver Matte</t>
         </is>
       </c>
       <c r="K123" s="3" t="n"/>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>Panthera Metal; Pebble Gray; Aurora Black Pearl; Snow White Pearl; Ocean Blue Pearl</t>
+          <t>Panthera Metallic; Pebble Gray; Aurora Black Pearl; Snow White Pearl; Ocean Blue Pearl; Pebble Grey</t>
         </is>
       </c>
       <c r="K124" s="3" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>Diamond White; Dsat Silver</t>
+          <t>Diamond White; Dsat Silver; Rocky Beige; Stealth Black</t>
         </is>
       </c>
       <c r="K125" s="3" t="n">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Black; Dsat Silver; Molten Red Rage; Pearl White</t>
+          <t>Black; Dsat Silver; Molten Red Rage; Pearl White; Stealth Black; Red Rage; Galaxy Grey; Everest White; Diamond White</t>
         </is>
       </c>
       <c r="K126" s="3" t="n">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>Dune Beige; Everest White; Stealth Black Plus G; Stealth Black; Dune Beige Plus Stea; Nebula Blue Plus Gal; Galaxy Grey Plus Ste; Tango Red Plus Steal</t>
+          <t>Dune Beige; Everest White; Stealth Black Plus G; Stealth Black; Dune Beige Plus Stea; Nebula Blue Plus Gal; Galaxy Grey Plus Ste; Tango Red Plus Steal; Deep Forest; Citrine Yellow</t>
         </is>
       </c>
       <c r="K128" s="3" t="n">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>Red Rage; Aqua Marine; Blazing Bronze; Everest White; Galaxy Grey; Napoli Black</t>
+          <t>Red Rage; Aqua Marine; Blazing Bronze; Everest White; Galaxy Grey; Napoli Black; Tango Red; Stealth Black; Battleship Grey Black; Deep Forest</t>
         </is>
       </c>
       <c r="K129" s="3" t="n">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>Everest White; Electic Blue; Dazzling Silv; Midnight Blac; Red Rage Dt; Electric Blue; Red Rage; Deep Forest; Burnt Sienna; Napoli Black; Blaze Red</t>
+          <t>Everest White; Electic Blue; Dazzling Silver; Midnight Black; Red Rage Dt; Electric Blue; Red Rage; Deep Forest; Burnt Sienna; Napoli Black; Blaze Red</t>
         </is>
       </c>
       <c r="K130" s="3" t="n">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>Designer Grey; Fiery Orange; Flamboyant Red; Flamboyant Red &amp; Met; Midnight black; Pearl White; Dazzling Silver &amp; Me</t>
+          <t>Designer Grey; Fiery Orange; Flamboyant Red; Flamboyant Red &amp; Metallic; Midnight black; Pearl White; Dazzling Silver &amp; Me</t>
         </is>
       </c>
       <c r="K131" s="3" t="n">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Rocky Beige; Diamond White; Highway Red; Majestic Silver; Napoli Black</t>
+          <t>Rocky Beige; Diamond White; Highway Red; Majestic Silver; Napoli Black; Jeans Blue; Concrete Grey; Pearl White; Stealth Black</t>
         </is>
       </c>
       <c r="K134" s="3" t="n">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>Aqua Marine; Iceberg White; Mariner Maroon; Oceanic Black; Shimmering Silver</t>
+          <t>Aqua Marine; Iceberg White; Mariner Maroon; Oceanic Black; Shimmering Silver; Poseidon Purple</t>
         </is>
       </c>
       <c r="K135" s="3" t="n">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Deep Forest; Dazzling Silver; Everest White; Grand Canyon; Napoli Black; Red Rage; Midnight Black</t>
+          <t>Deep Forest; Dazzling Silver; Everest White; Grand Canyon; Napoli Black; Red Rage; Midnight Black; Valyrian Silver; Stealth Black</t>
         </is>
       </c>
       <c r="K136" s="3" t="n">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Everest White; Desert Myst; Deep Forest; Tango Red; Firestorm Orange; Napoli Black; Desert Myst Satin; Everest White Satin</t>
+          <t>Everest White; Desert Myst; Deep Forest; Tango Red; Firestorm Orange; Napoli Black; Desert Myst Satin; Everest White Satin; Stealth Black</t>
         </is>
       </c>
       <c r="K143" s="3" t="n">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>Everest White; Stealth Black; Nebula Blue; Battleship Gray; Deep Forest; Tango Red; Burnt Sienna</t>
+          <t>Everest White; Stealth Black; Nebula Blue; Battleship Gray; Deep Forest; Tango Red; Burnt Sienna; Burnt Sienna Black; Battleship Grey Black; Nebula Blue Black; Deep Forest Black; Everest White Black; Tango Red Black</t>
         </is>
       </c>
       <c r="K165" s="3" t="n"/>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>Silky silver; Poolside Blue; Pearl Metallic Nutme; Solid White; Prime-Gallant-Red; Magma Grey</t>
+          <t>Silky silver; Poolside Blue; Pearl Metallic Nutmeg; Solid White; Prime-Gallant-Red; Magma Grey; Gallant Red; Nutmeg Brown</t>
         </is>
       </c>
       <c r="K168" s="3" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>Pearl Arctic White; Pearl Metallic Lucen; Pearl Arctic White P; Metallic silky silve; Pearl Arctic White M; Solid Fire Red; Pearl Metallic Midni; Metallic Magma Grey</t>
+          <t>Pearl Arctic White; Pearl Metallic Lucent; Pearl Arctic White P; Metallic silky Silver; Pearl Arctic White M; Solid Fire Red; Pearl Metallic Midnight; Metallic Magma Grey; Splendid Silver; Magna Grey; Novel Orange; Luster Blue; Bluish Black; Sizzling Red</t>
         </is>
       </c>
       <c r="K169" s="3" t="n">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>Pearl Arctic White; Pearl Metallic Lucen; Pearl Arctic White P; Metallic silky silve; Pearl Arctic White M; Solid Fire Red; Pearl Metallic Midni; Metallic Magma Grey</t>
+          <t>Pearl Arctic White; Pearl Metallic Lucent; Pearl Arctic White P; Metallic silky Silver; Pearl Arctic White M; Solid Fire Red; Pearl Metallic Midnight; Metallic Magma Grey; Splendid Silver; Magna Grey; Novel Orange; Luster Blue; Bluish Black; Sizzling Red</t>
         </is>
       </c>
       <c r="K170" s="3" t="n">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>Pearl Arctic White; Pearl Metallic Lucen; Pearl Arctic White P; Metallic silky silve; Pearl Arctic White M; Solid Fire Red; Pearl Metallic Midni; Metallic Magma Grey</t>
+          <t>Pearl Arctic White; Pearl Metallic Lucent; Pearl Arctic White P; Metallic silky Silver; Pearl Arctic White M; Solid Fire Red; Pearl Metallic Midnight; Metallic Magma Grey; Splendid Silver; Magna Grey; Novel Orange; Luster Blue; Bluish Black; Sizzling Red</t>
         </is>
       </c>
       <c r="K171" s="3" t="n">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>Pearl Arctic White; Pearl Metallic Lucen; Pearl Arctic White P; Metallic silky silve; Pearl Arctic White M; Solid Fire Red; Pearl Metallic Midni; Metallic Magma Grey</t>
+          <t>Pearl Arctic White; Pearl Metallic Lucent; Pearl Arctic White P; Metallic silky Silver; Pearl Arctic White M; Solid Fire Red; Pearl Metallic Midnight; Metallic Magma Grey; Splendid Silver; Magna Grey; Novel Orange; Luster Blue; Bluish Black; Sizzling Red</t>
         </is>
       </c>
       <c r="K172" s="3" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>Pearl Arctic White; Pearl Metallic Lucen; Pearl Arctic White P; Metallic silky silve; Pearl Arctic White M; Solid Fire Red; Pearl Metallic Midni; Metallic Magma Grey</t>
+          <t>Pearl Arctic White; Pearl Metallic Lucent; Pearl Arctic White P; Metallic silky Silver; Pearl Arctic White M; Solid Fire Red; Pearl Metallic Midnight; Metallic Magma Grey; Splendid Silver; Magna Grey; Novel Orange; Luster Blue; Bluish Black; Sizzling Red</t>
         </is>
       </c>
       <c r="K173" s="3" t="n">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>Pearl Arctic White; Pearl Phoenix Red; Metallic Premium sil; Blue</t>
+          <t>Pearl Arctic White; Pearl Phoenix Red; Metallic Premium Silver; Blue</t>
         </is>
       </c>
       <c r="K179" s="3" t="n">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>Pearl Arctic White; Pearl Phoenix Red; Metallic Premium sil; Blue</t>
+          <t>Pearl Arctic White; Pearl Phoenix Red; Metallic Premium Silver; Blue</t>
         </is>
       </c>
       <c r="K180" s="3" t="n">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>Pearl Arctic White; Pearl Phoenix Red; Metallic Premium sil; Blue</t>
+          <t>Pearl Arctic White; Pearl Phoenix Red; Metallic Premium Silver; Blue</t>
         </is>
       </c>
       <c r="K181" s="3" t="n">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>Pearl Arctic White; Metallic silky silve; Pearl Metallic Aubur; Pearl Metallic Oxfor; Metallic Magma Grey</t>
+          <t>Pearl Arctic White; Metallic silky Silver; Pearl Metallic Aubur; Pearl Metallic Oxford; Metallic Magma Grey; Bluish Black; Dignity Brown; Oxford Blue; Auburn Red; Magma Grey; Splendid Silver</t>
         </is>
       </c>
       <c r="K182" s="3" t="n">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>Torque Blue; Arctic White; Blazing Red; Silky silver; Tango Orange</t>
+          <t>Torque Blue; Arctic White; Blazing Red; Silky silver; Tango Orange; Speedy Blue; Fire Red; Caffeine Brown; White; Glistening Grey</t>
         </is>
       </c>
       <c r="K184" s="3" t="n">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>Breeze Blue; Metallic Glistening; Metallic silky silve; Pearl Midnight Black; Solid White</t>
+          <t>Breeze Blue; Metallic Glistening; Metallic silky silve; Pearl Midnight Black; Solid White; Glistening Grey; Silky Silver; Cerulean Blue</t>
         </is>
       </c>
       <c r="K185" s="3" t="n">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>Metallic Granite Gre; Metallic silky silve; Metallic Sizzling Re; Metallic Speedy Blue; Premium Earth Gold; Solid White</t>
+          <t>Metallic Granite Gre; Metallic silky silve; Metallic Sizzling Re; Metallic Speedy Blue; Premium Earth Gold; Solid White; Silky Silver; Earth Gold; Sizzling Red; Granite Grey</t>
         </is>
       </c>
       <c r="K186" s="3" t="n">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>Sizzling Red; Brave Khaki; Exuberant Blue; Magma Grey; Pearl Arctic White; Splendid Silver</t>
+          <t>Sizzling Red; Brave Khaki; Exuberant Blue; Magma Grey; Pearl Arctic White; Splendid Silver; Pearl Midnight Black</t>
         </is>
       </c>
       <c r="K187" s="3" t="n">
@@ -8759,7 +8759,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Arctic White Midnigh; Arctic White; Chestnut Brown; Grandeur Grey; Midnight black; Nexa Blue; Opulent Red; Opulent Red Midnight; Splendid Silver Midn; Splendid Silver</t>
+          <t>Arctic White Midnight; Arctic White; Chestnut Brown; Grandeur Grey; Midnight black; Nexa Blue; Opulent Red; Opulent Red Midnight; Splendid Silver Midnight; Splendid Silver; Celestial Blue; Granite Grey</t>
         </is>
       </c>
       <c r="K188" s="3" t="n">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>Magma Grey; Nexa Blue; Pearl Metallic Digni; Pearl Midnight Black; Pearl Sangria Red; Pearl Snow White; Silver Metalic</t>
+          <t>Magma Grey; Nexa Blue; Pearl Metallic Dignity; Pearl Midnight Black; Pearl Sangria Red; Pearl Snow White; Silver Metalic; Premium Silver; Dignity Brown; Sangria Red; Midnight Black; Magma Gray; Snow White; Silver Metallic</t>
         </is>
       </c>
       <c r="K189" s="3" t="n">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>Nexa Blue; Glistening Grey; Lucent Orange; Pearl White; Silky silver; Turquoise Blue</t>
+          <t>Nexa Blue; Glistening Grey; Lucent Orange; Pearl White; Silky silver; Turquoise Blue; Pearl Arctic White; Bluish Black</t>
         </is>
       </c>
       <c r="K192" s="3" t="n">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>Nexa Blue; Glistening Grey; Lucent Orange; Pearl White; Silky silver; Turquoise Blue</t>
+          <t>Nexa Blue; Glistening Grey; Lucent Orange; Pearl White; Silky silver; Turquoise Blue; Pearl Arctic White; Bluish Black</t>
         </is>
       </c>
       <c r="K193" s="3" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>Nexa Blue; Arctic White; Earthen Brown; Grandeur Grey; Opulent Red; Splendid Silver</t>
+          <t>Nexa Blue; Arctic White; Earthen Brown; Grandeur Grey; Opulent Red; Splendid Silver; Bluish Black</t>
         </is>
       </c>
       <c r="K195" s="3" t="n">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>Metallic Graphite Gr; Metallic silky silve; Pearl Starry Blue; Solid Fire Red; Solid Sizzle Orange</t>
+          <t>Metallic Graphite Gr; Metallic silky silve; Pearl Starry Blue; Solid Fire Red; Solid Sizzle Orange; Sizzle Orange; Granite Grey; Silky Silver; Solid Superior White</t>
         </is>
       </c>
       <c r="K196" s="3" t="n">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>Artic White; Auburn Red; Brave Khaki; Megma Grey; Nexa Blue; Premium Silver</t>
+          <t>Artic White; Auburn Red; Brave Khaki; Megma Grey; Nexa Blue; Premium Silver; Arctic White; Opulent Red; Grandeur Grey; Splendid Silver</t>
         </is>
       </c>
       <c r="K198" s="3" t="n">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>Aurora Silver; Candy White; Dune Brown; Glaze Red; Havana Grey; Starry Black</t>
+          <t>Aurora Silver; Candy White; Dune Brown; Glaze Red; Havana Grey; Starry Black; Celadon Blue; Pearl White</t>
         </is>
       </c>
       <c r="K213" s="3" t="n">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>Aurora Silver; Candy White; Dune Brown; Glaze Red; Havana Grey; Starry Black</t>
+          <t>Aurora Silver; Candy White; Dune Brown; Glaze Red; Havana Grey; Starry Black; Celadon Blue; Pearl White</t>
         </is>
       </c>
       <c r="K214" s="3" t="n">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>Aurora Silver; Candy White; Dune Brown; Glaze Red; Havana Grey; Starry Black</t>
+          <t>Aurora Silver; Candy White; Dune Brown; Glaze Red; Havana Grey; Starry Black; Celadon Blue; Pearl White</t>
         </is>
       </c>
       <c r="K215" s="3" t="n">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>Aurora Silver; Candy White; Dune Brown; Glaze Red; Havana Grey; Starry Black</t>
+          <t>Aurora Silver; Candy White; Dune Brown; Glaze Red; Havana Grey; Starry Black; Celadon Blue; Pearl White</t>
         </is>
       </c>
       <c r="K216" s="3" t="n">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>Pearl Whi; Turquoise; Aurora Si; Starburst; Glaze Red; Celadon B</t>
+          <t>Pearl White; Turquoise; Aurora Silver; Starburst; Glaze Red; Celadon Blue; Clay Beige; Turquoise Green; Starburst Black</t>
         </is>
       </c>
       <c r="K218" s="3" t="n">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>Blue; Currant Red; Ashen Silver; Ferris White; Sable Black</t>
+          <t>Blue; Currant Red; Ashen Silver; Ferris White; Sable Black; Candy White; Starry Black; Aurora Silver; Glaze Red</t>
         </is>
       </c>
       <c r="K219" s="3" t="n">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>Blue; Currant Red; Ashen Silver; Ferris White; Sable Black</t>
+          <t>Blue; Currant Red; Ashen Silver; Ferris White; Sable Black; Candy White; Starry Black; Aurora Silver; Glaze Red</t>
         </is>
       </c>
       <c r="K220" s="3" t="n">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>Copper Orang; Blade Silver; Onyx Black; Vivid Blue &amp;; Pearl White; Fire Granet</t>
+          <t>Copper Orange; Blade Silver; Onyx Black; Vivid Blue &amp;; Pearl White; Fire Granet; Sunrise Copper Orange; Storm White; Metallic Grey; Flare Garnet Red</t>
         </is>
       </c>
       <c r="K230" s="3" t="n">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>Bronze; Champagne Gold; Diamond Black; Diamond Silver; Pearl White; Sapphire Blue</t>
+          <t>Bronze; Champagne Gold; Diamond Black; Diamond Silver; Pearl White; Sapphire Blue; Champagne Silver</t>
         </is>
       </c>
       <c r="K236" s="3" t="n">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>Black Metallic; Blue Racing; Gun Metalli; Katsura Orange; Pearl White; Ultimate Silver; Vibrant Red</t>
+          <t>Black Metallic; Blue Racing; Gun Metallic; Katsura Orange; Pearl White; Ultimate Silver; Vibrant Red</t>
         </is>
       </c>
       <c r="K237" s="3" t="n">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>Fiery Red; Metal Mustard Black; Ice Cool White; Moonlight Silver; Zanskar Blue; Zanskar Blue Black R; Outback Bronze</t>
+          <t>Fiery Red; Metal Mustard Black; Ice Cool White; Moonlight Silver; Zanskar Blue; Zanskar Blue Black R; Outback Bronze; Electric Blue</t>
         </is>
       </c>
       <c r="K245" s="3" t="n">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>Caspian Blue Metalli; Cayenne Orange; Mahogany Brown; Moonlight Silver; Outback Bronze; Pearl White; Slate Grey</t>
+          <t>Caspian Blue Metallic; Cayenne Orange; Mahogany Brown; Moonlight Silver; Outback Bronze; Pearl White; Slate Grey; Sunset Red; Stealth Black; River Blue; Mountain Jade Green</t>
         </is>
       </c>
       <c r="K246" s="3" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>Moonlight Silver; Ice Cool White; Cedar Brown; Stealth Black; Metal Mustard</t>
+          <t>Moonlight Silver; Ice Cool White; Cedar Brown; Stealth Black; Metal Mustard; Amber Terracotta; Shadow Grey; Zanskar Blue</t>
         </is>
       </c>
       <c r="K247" s="3" t="n">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>Radiant Red; Caspian Blue; Ice Cool White; Mahogany Brown; Moonlight Silver</t>
+          <t>Radiant Red; Caspian Blue; Ice Cool White; Mahogany Brown; Moonlight Silver; Stealth Black</t>
         </is>
       </c>
       <c r="K248" s="3" t="n">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>Honey Orange; Candy-White-With-Car; Carbon Steel; Tornado Red; Brilliant Silver; Candy White; Onyx; Tornado-Red-With-Car</t>
+          <t>Honey Orange; Candy-White-With-Car; Carbon Steel; Tornado Red; Brilliant Silver; Candy White; Onyx; Tornado-Red-With-Car; Steel Grey; Shimla Green; Cherry Red; Deep Black; Lava Blue</t>
         </is>
       </c>
       <c r="K256" s="3" t="n">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>Crystal Blue; Candy White; Carbon Steel; Tornado Red; Toreador Red; Brilliant Silver; Platinum White Pearl</t>
+          <t>Crystal Blue; Candy White; Carbon Steel; Tornado Red; Toreador Red; Brilliant Silver; Platinum White Pearl; Lava Blue; Deep Black</t>
         </is>
       </c>
       <c r="K257" s="3" t="n">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>Business Grey Metall; Lava Blue; Magic Black; Magnetic Brown; Moon White; Brilliant Silver; Graphite Grey</t>
+          <t>Business Grey Metallic; Lava Blue; Magic Black; Magnetic Brown; Moon White; Brilliant Silver; Graphite Grey</t>
         </is>
       </c>
       <c r="K260" s="3" t="n">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>Brilliant Silv; Lava Blue; Olive Gold; Carbon Steel; Deep Black Pea; Tornado Red; Candy White</t>
+          <t>Brilliant Silver; Lava Blue; Olive Gold; Carbon Steel; Deep Black Pea; Tornado Red; Candy White</t>
         </is>
       </c>
       <c r="K262" s="3" t="n">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>Steel Grey; Moon White; Bronx Gold; Magic Black; Graphite Grey; Race Blue; Velvet Red</t>
+          <t>Steel Grey; Moon White; Bronx Gold; Magic Black; Graphite Grey; Race Blue; Velvet Red; Black Magic</t>
         </is>
       </c>
       <c r="K264" s="3" t="n">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>Fiery Red; Denim Blue; Phantom Black; Polar White; Titan Grey; Typhoon Silver</t>
+          <t>Fiery Red; Denim Blue; Phantom Black; Polar White; Titan Grey; Typhoon Silver; Calgary White; Pristine White; Daytona Grey; Flame Red; Pure Grey; Creative Ocean; Fearless Purple</t>
         </is>
       </c>
       <c r="K267" s="3" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>Arizona Blue; Daytona Grey; Flam Red; Pearlescent White; Pure Silver; Tornado Blue; Ocean Blue; Pristine White; Supernova Coper</t>
+          <t>Arizona Blue; Daytona Grey; Flam Red; Pearlescent White; Pure Silver; Tornado Blue; Ocean Blue; Pristine White; Supernova Coper; Pure Grey; Sobo Surge; Pangong Pulse; Varanasi Vibrance; Supernova Copper</t>
         </is>
       </c>
       <c r="K268" s="3" t="n">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>Tornado Blue; Tropical Mist; Orcus White; Calypso Red; Daytona Grey; Foliage Green; Meteor Bronze; Atomic Orange</t>
+          <t>Tornado Blue; Tropical Mist; Orcus White; Calypso Red; Daytona Grey; Foliage Green; Meteor Bronze; Atomic Orange; Caramel; Cyantafic Blue; Coorg Clouds; Bengal Rouge; Pristine White</t>
         </is>
       </c>
       <c r="K269" s="3" t="n">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>Ember Glow; Pristine Whit; Pure Grey; Dune GLow; Royal Blue</t>
+          <t>Ember Glow; Pristine White; Pure Grey; Dune GLow; Royal Blue; Royale Blue</t>
         </is>
       </c>
       <c r="K270" s="3" t="n">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>Ember Glow; Pristine Whit; Pure Grey; Dune GLow; Royal Blue</t>
+          <t>Ember Glow; Pristine White; Pure Grey; Dune GLow; Royal Blue; Royale Blue</t>
         </is>
       </c>
       <c r="K271" s="3" t="n">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>Oberon Black; Stardust Ash; Lunar Slate; Cosmic Gold; Galactic Sapphire; Supernova Coper; Stellar Frost</t>
+          <t>Oberon Black; Stardust Ash; Lunar Slate; Cosmic Gold; Galactic Sapphire; Supernova Coper; Stellar Frost; Stealer Frost; Supernova Copper</t>
         </is>
       </c>
       <c r="K275" s="3" t="n">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>Oberon Black; Pebble Gray; Seaweed Green; Sunlit Yellow Black; Sunlit Yellow; Ash Gray; Coral Red; Black</t>
+          <t>Oberon Black; Pebble Gray; Seaweed Green; Sunlit Yellow Black; Sunlit Yellow; Ash Gray; Coral Red; Black; Pebble Grey; Lunar White</t>
         </is>
       </c>
       <c r="K277" s="3" t="n">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>Oberon Black; Pebble Gray; Seaweed Green; Sunlit Yellow Black; Sunlit Yellow; Ash Gray; Coral Red; Black</t>
+          <t>Oberon Black; Pebble Gray; Seaweed Green; Sunlit Yellow Black; Sunlit Yellow; Ash Gray; Coral Red; Black; Pebble Grey; Lunar White</t>
         </is>
       </c>
       <c r="K278" s="3" t="n">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>Oberon Black; Pebble Gray; Seaweed Green; Sunlit Yellow Black; Sunlit Yellow; Ash Gray; Coral Red; Black</t>
+          <t>Oberon Black; Pebble Gray; Seaweed Green; Sunlit Yellow Black; Sunlit Yellow; Ash Gray; Coral Red; Black; Pebble Grey; Lunar White</t>
         </is>
       </c>
       <c r="K279" s="3" t="n">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>Pristine White; Empowered Oxide; Flame Red; Daytona Grey; Intensi Teal; Ocean Blue; Purpal</t>
+          <t>Pristine White; Empowered Oxide; Flame Red; Daytona Grey; Intensi Teal; Ocean Blue; Purpal; Intensi-Teal; Creative Ocean; Fearless Purple</t>
         </is>
       </c>
       <c r="K281" s="3" t="n">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>Tropical Mist; Teal Blue; Pristine White; Midnight Plum; Daytona Grey</t>
+          <t>Tropical Mist; Teal Blue; Pristine White; Midnight Plum; Daytona Grey; Pure Grey; Pangong Pulse; Sobo Surge; Dehradun Dew</t>
         </is>
       </c>
       <c r="K284" s="3" t="n">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>Daytona Grey; Magnetic Red; Signature Teal Blue</t>
+          <t>Daytona Grey; Magnetic Red; Signature Teal Blue; Pristine White; Midnight Plum; Teal Blue</t>
         </is>
       </c>
       <c r="K291" s="3" t="n">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>Virtual Sun; Flame Red; Pristine Wh; Pure Grey; Empowered O</t>
+          <t>Virtual Sunrise; Flame Red; Pristine White; Pure Grey; Empowered Oxide</t>
         </is>
       </c>
       <c r="K297" s="3" t="n"/>
@@ -13551,7 +13551,7 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>Nainital; Pristine; Pure Grey; Empowered</t>
+          <t>Nainital; Pristine; Pure Grey; Empowered; Nainital Nocturne; Empowered Oxide; Pristine White</t>
         </is>
       </c>
       <c r="K298" s="3" t="n"/>
@@ -13774,7 +13774,7 @@
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>Plati; Attit; Black; Silve; Super; Avant</t>
+          <t>Platinum White Pearl; Attitude Black Mica; Blackish Ageha; Silver Metallic; Super; Avant; Super White; Avant-Garde Bronze; Sparkling Black Pearl</t>
         </is>
       </c>
       <c r="K303" s="3" t="n">
@@ -13819,7 +13819,7 @@
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>Avant garde bronze; Garnet Red; Grey; Silver; Sparkling Black Crys; Super white; Attitude Black; White Pearl Crystal</t>
+          <t>Avant garde bronze; Garnet Red; Grey; Silver; Sparkling Black Crystal; Super white; Attitude Black; White Pearl Crystal; Platinum White Pearl; Silver Metallic; Avant-Garde Bronze</t>
         </is>
       </c>
       <c r="K304" s="3" t="n">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>Phantom Bro; Platinum Wh; Sparkling B; Avant Garde; Attitude Bl; Silver Meta; Super White</t>
+          <t>Phantom Brown; Platinum White Pearl; Sparkling Black; Avant Garde; Attitude Black; Silver Metallic; Super White; Avant-Garde Bronze</t>
         </is>
       </c>
       <c r="K305" s="3" t="n">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="J313" s="2" t="inlineStr">
         <is>
-          <t>Spunky Blue; Cafe White; Conic Grey; Enticing Silver; Rustic Brown</t>
+          <t>Spunky Blue; Cafe White; Conic Grey; Enticing Silver; Rustic Brown; Iconic Grey</t>
         </is>
       </c>
       <c r="K313" s="3" t="n">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="J315" s="2" t="inlineStr">
         <is>
-          <t>Red Mica Metallic; Attitude Black; Graphite; Platinum White Pearl; Silver Metallic; Precious Metal; Emotional Red; Dark Blue; Cement Grey</t>
+          <t>Red Mica Metallic; Attitude Black; Graphite; Platinum White Pearl; Silver Metallic; Precious Metallic; Emotional Red; Dark Blue; Cement Grey</t>
         </is>
       </c>
       <c r="K315" s="3" t="n">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="J316" s="2" t="inlineStr">
         <is>
-          <t>Platinum White Pearl; Precious Metal; Black</t>
+          <t>Platinum White Pearl; Precious Metallic; Black; Silver Mica Metallic; New Pearl White</t>
         </is>
       </c>
       <c r="K316" s="3" t="n">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="J317" s="2" t="inlineStr">
         <is>
-          <t>White Pearl Crystal; Emotional Red; Grey Metallic; Super White; Attitude Black</t>
+          <t>White Pearl Crystal; Emotional Red; Grey Metallic; Super White; Attitude Black; White Pearl Crystal Shine; Black</t>
         </is>
       </c>
       <c r="K317" s="3" t="n">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="J329" s="2" t="inlineStr">
         <is>
-          <t>Nightshade Blue; Deep black; Dolphin Grey; Kings Red; Oryx White; Pure white; Reflex Silver</t>
+          <t>Nightshade Blue; Deep black; Dolphin Grey; Kings Red; Oryx White; Pure white; Reflex Silver; Grenadilla Black; Cipressino Green; Oyster Silver; Persimmon Red</t>
         </is>
       </c>
       <c r="K329" s="3" t="n">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>Kurkuma Yellow; Ruby Red Metallic; Pure white; Deep Black Pearl; Petroleum Blue; Habanero Orange; Platinum Gray Metall; Pyrit Silver</t>
+          <t>Kurkuma Yellow; Ruby Red Metallic; Pure white; Deep Black Pearl; Petroleum Blue; Habanero Orange; Platinum Gray Metallic; Pyrit Silver</t>
         </is>
       </c>
       <c r="K331" s="3" t="n">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
-          <t>Oryx White; Grenadilla; Moonstone G; Kings Red P</t>
+          <t>Oryx White; Grenadilla; Moonstone Grey; Kings Red P; Grenadilla Black</t>
         </is>
       </c>
       <c r="K334" s="3" t="n">
@@ -43617,7 +43617,7 @@
       </c>
       <c r="J1042" s="2" t="inlineStr">
         <is>
-          <t>Fire Red; Foresta Green; Cloudy Gray; Polar White</t>
+          <t>Fire Red; Foresta Green; Cloudy Gray; Polar White; Cloudy Grey</t>
         </is>
       </c>
       <c r="K1042" s="3" t="n"/>
@@ -43658,7 +43658,7 @@
       </c>
       <c r="J1043" s="2" t="inlineStr">
         <is>
-          <t>Nexa Blue; Majestic Silver; Mystic White; Stellar Bronze</t>
+          <t>Nexa Blue; Majestic Silver; Mystic White; Stellar Bronze; Titan Grey; Hazel Blue; Dragon Red; Atlas White; Abyss Black</t>
         </is>
       </c>
       <c r="K1043" s="3" t="n"/>
@@ -43740,7 +43740,7 @@
       </c>
       <c r="J1045" s="2" t="inlineStr">
         <is>
-          <t>Blue Black; Polar White; Starry Night; Abyss Black; Thunder Blue; Titan Grey</t>
+          <t>Blue Black; Polar White; Starry Night; Abyss Black; Thunder Blue; Titan Grey; Pearl White; Blue-Black</t>
         </is>
       </c>
       <c r="K1045" s="3" t="n"/>
@@ -43863,7 +43863,7 @@
       </c>
       <c r="J1048" s="2" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>White; Diamond White; Majestic Silver; Napoli Black</t>
         </is>
       </c>
       <c r="K1048" s="3" t="n"/>
@@ -44068,7 +44068,7 @@
       </c>
       <c r="J1053" s="2" t="inlineStr">
         <is>
-          <t>Pl</t>
+          <t>Platinum White Pearl</t>
         </is>
       </c>
       <c r="K1053" s="3" t="n"/>
